--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
@@ -912,69 +912,69 @@
   </si>
   <si>
     <t>214
-151</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>R$ 727.194,12</t>
-  </si>
-  <si>
-    <t>R$ 4.573,55
-R$ 4.665,43</t>
-  </si>
-  <si>
-    <t>2.5%
-4.6%</t>
-  </si>
-  <si>
-    <t>49.8</t>
+170</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R$ 810.682,22</t>
+  </si>
+  <si>
+    <t>R$ 4.503,79
+R$ 4.583,23</t>
+  </si>
+  <si>
+    <t>2.7%
+4.5%</t>
+  </si>
+  <si>
+    <t>49.3</t>
   </si>
   <si>
     <t>(3.2%)</t>
   </si>
   <si>
-    <t>100.1%</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>73.2%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
+    <t>94.9%</t>
+  </si>
+  <si>
+    <t>54.9%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>26.1</t>
+  </si>
+  <si>
+    <t>73.0%</t>
+  </si>
+  <si>
+    <t>8.1%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>6.5</t>
+    <t>6.7</t>
   </si>
   <si>
     <t>11.4</t>
   </si>
   <si>
-    <t>17.8</t>
-  </si>
-  <si>
-    <t>76.8%</t>
-  </si>
-  <si>
-    <t>-R$ 25.243,68</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>75.7%</t>
+  </si>
+  <si>
+    <t>-R$ 28.969,47</t>
+  </si>
+  <si>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -3094,10 +3094,10 @@
         <v>-0.10483870967741937</v>
       </c>
       <c r="T14" s="6">
-        <v>0.2998591567013541</v>
+        <v>0.34035220017456635</v>
       </c>
       <c r="U14" s="6">
-        <v>-0.0070215053347241867</v>
+        <v>0.033471538138488008</v>
       </c>
       <c r="V14" s="6">
         <v>0.031122837032062534</v>
@@ -4709,7 +4709,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4745,25 +4745,59 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
+      <c r="O27" s="5">
+        <v>4662.8999999999996</v>
+      </c>
+      <c r="P27" s="5">
+        <v>4662.8999999999996</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.16258847066302939</v>
+      </c>
+      <c r="R27" s="7">
+        <v>49</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.27941176470588236</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.29024296038945724</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.042742949666516546</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.034524223122949241</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.024551888309850094</v>
+      </c>
+      <c r="X27" s="8">
+        <v>34.115054838709682</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>3.8006937500000002</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>12.796235483870968</v>
+      </c>
       <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="AD27" s="8">
+        <v>19.009999999999998</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.61290322580645162</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>-146.69999999999999</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4804,7 +4838,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4840,25 +4874,59 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
+      <c r="O28" s="5">
+        <v>6102.8100000000004</v>
+      </c>
+      <c r="P28" s="5">
+        <v>6102.8100000000004</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.54082570428758281</v>
+      </c>
+      <c r="R28" s="7">
+        <v>69</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="T28" s="6">
+        <v>7.7783840558693447E-05</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.33097463299693086</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.070670314166752693</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.062860796911586622</v>
+      </c>
+      <c r="X28" s="8">
+        <v>27.980458620689657</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>4.4909308823529415</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>6.9856310344827586</v>
+      </c>
       <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="AD28" s="8">
+        <v>18.710920689655175</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.62068965517241381</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-882.5</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -6173,7 +6241,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6209,25 +6277,59 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
+      <c r="O39" s="5">
+        <v>4815.5600000000004</v>
+      </c>
+      <c r="P39" s="5">
+        <v>4815.5600000000004</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.15104825235501229</v>
+      </c>
+      <c r="R39" s="7">
+        <v>58</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.074074074074074181</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.27598391464336441</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.032532644178454841</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.10439772321391488</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.058467447192019198</v>
+      </c>
+      <c r="X39" s="8">
+        <v>18.610099999999999</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.2111105263157893</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>3.3333347826086959</v>
+      </c>
       <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="AD39" s="8">
+        <v>11.290403030303031</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.96969696969696972</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6530,7 +6632,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6566,25 +6668,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>5055.1099999999997</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5055.1099999999997</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.00041361403675410635</v>
+      </c>
+      <c r="R42" s="7">
+        <v>46</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.14814814814814814</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.28875545734909824</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.011089887262591715</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.050172399809301882</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0066303206062776092</v>
+      </c>
+      <c r="X42" s="8">
+        <v>30.810647222222219</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.3989361702127656</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>11.131480555555555</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>26.162963888888889</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7018,7 +7154,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -7052,25 +7188,57 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="O46" s="5">
+        <v>6231.1700000000001</v>
+      </c>
+      <c r="P46" s="5">
+        <v>6231.1700000000001</v>
+      </c>
       <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
+      <c r="R46" s="7">
+        <v>67</v>
+      </c>
+      <c r="S46" s="6">
+        <v>0.39583333333333326</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.37297761094625886</v>
+      </c>
+      <c r="U46" s="6">
+        <v>-0.00044182713679774424</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.062782109940829736</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.024711891988181994</v>
+      </c>
+      <c r="X46" s="8">
+        <v>43.511787804878054</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0.46341463414634149</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>9.4674353846153849</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>16.091463414634145</v>
+      </c>
       <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="AD46" s="8">
+        <v>34.68292682926829</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.14634146341463414</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>864.20000000000005</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7500,7 +7668,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7536,25 +7704,59 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
+      <c r="O50" s="5">
+        <v>6193.0500000000002</v>
+      </c>
+      <c r="P50" s="5">
+        <v>6193.0500000000002</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0.66134172447649253</v>
+      </c>
+      <c r="R50" s="7">
+        <v>68</v>
+      </c>
+      <c r="S50" s="6">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.26501571923365708</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.07461822526864792</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.046766617417912014</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.0084252508860739039</v>
+      </c>
+      <c r="X50" s="8">
+        <v>23.195613157894737</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.644624193548387</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>4.9245605263157897</v>
+      </c>
       <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="AD50" s="8">
+        <v>15.41622894736842</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.86842105263157898</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -8081,7 +8283,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8117,25 +8319,59 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
+      <c r="O55" s="5">
+        <v>3917.71</v>
+      </c>
+      <c r="P55" s="5">
+        <v>3917.71</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.01244492170563738</v>
+      </c>
+      <c r="R55" s="7">
+        <v>48</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.076923076923076872</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.34003282529845241</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.10120491307421937</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.038693905368187023</v>
+      </c>
+      <c r="X55" s="8">
+        <v>26.829823684210528</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.078947368421052627</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.3327037735849054</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>6.7692973684210527</v>
+      </c>
       <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="AD55" s="8">
+        <v>16.600876315789474</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.71052631578947367</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -10055,7 +10291,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -10089,25 +10325,59 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
+      <c r="O71" s="5">
+        <v>4873.5500000000002</v>
+      </c>
+      <c r="P71" s="5">
+        <v>4873.5500000000002</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.089599556428985094</v>
+      </c>
+      <c r="R71" s="7">
+        <v>68</v>
+      </c>
+      <c r="S71" s="6">
+        <v>0.19298245614035081</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.25467829405669379</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.059938361153573878</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.063155297473094563</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.0096357891065034732</v>
+      </c>
+      <c r="X71" s="8">
+        <v>22.630106451612907</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>2.2982046153846154</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>6.5472233333333332</v>
+      </c>
       <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="AD71" s="8">
+        <v>16.266667741935485</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.83870967741935487</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10497,7 +10767,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10533,25 +10803,59 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
+      <c r="O75" s="5">
+        <v>3059.2600000000002</v>
+      </c>
+      <c r="P75" s="5">
+        <v>3059.2600000000002</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.21648644910796144</v>
+      </c>
+      <c r="R75" s="7">
+        <v>33</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.19512195121951215</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32509168883978473</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.066422925805586966</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.032417970358844944</v>
+      </c>
+      <c r="X75" s="8">
+        <v>26.086363636363636</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>3.858853125</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>8.7257545454545458</v>
+      </c>
       <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="AD75" s="8">
+        <v>19.5303</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.63636363636363635</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-102.05</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -12306,7 +12610,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12342,25 +12646,59 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
+      <c r="O90" s="5">
+        <v>3093.0300000000002</v>
+      </c>
+      <c r="P90" s="5">
+        <v>3093.0300000000002</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>1.0155678789498039</v>
+      </c>
+      <c r="R90" s="7">
+        <v>34</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="T90" s="6">
+        <v>9.0972611646185122</v>
+      </c>
+      <c r="U90" s="6">
+        <v>5.4412054522587878</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.19567091169500456</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.13295571009657195</v>
+      </c>
+      <c r="X90" s="8">
+        <v>30.468839130434784</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.086956521739130432</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>4.320706060606061</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>14.029708695652173</v>
+      </c>
       <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="AD90" s="8">
+        <v>25.385508695652174</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.65217391304347827</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-373.43000000000001</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12532,7 +12870,7 @@
         <v>19700</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C92" s="4">
         <v>44</v>
@@ -12568,25 +12906,49 @@
       <c t="s" r="N92" s="4">
         <v>52</v>
       </c>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="7"/>
-      <c r="S92" s="6"/>
-      <c r="T92" s="6"/>
-      <c r="U92" s="6"/>
-      <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
+      <c r="O92" s="5">
+        <v>2794.5300000000002</v>
+      </c>
+      <c r="P92" s="5">
+        <v>2794.5300000000002</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>-0.058789254583911377</v>
+      </c>
+      <c r="R92" s="7">
+        <v>34</v>
+      </c>
+      <c r="S92" s="6">
+        <v>-0.17073170731707321</v>
+      </c>
+      <c r="T92" s="6">
+        <v>0</v>
+      </c>
+      <c r="U92" s="6">
+        <v>-0.33870454065621047</v>
+      </c>
+      <c r="V92" s="6">
+        <v>0.21549419759315519</v>
+      </c>
+      <c r="W92" s="6">
+        <v>0.19940920297867618</v>
+      </c>
       <c r="X92" s="8"/>
-      <c r="Y92" s="6"/>
+      <c r="Y92" s="6">
+        <v>0.052631578947368418</v>
+      </c>
       <c r="Z92" s="6"/>
-      <c r="AA92" s="8"/>
+      <c r="AA92" s="8">
+        <v>4.2378378378378381</v>
+      </c>
       <c r="AB92" s="8"/>
       <c r="AC92" s="8"/>
       <c r="AD92" s="8"/>
       <c r="AE92" s="6"/>
       <c r="AF92" s="9"/>
-      <c r="AG92" s="5"/>
+      <c r="AG92" s="5">
+        <v>0</v>
+      </c>
       <c r="AH92" s="10">
         <v>3</v>
       </c>
@@ -14603,7 +14965,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14637,25 +14999,59 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
+      <c r="O109" s="5">
+        <v>4415.3500000000004</v>
+      </c>
+      <c r="P109" s="5">
+        <v>4415.3500000000004</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>-0.059617444790182494</v>
+      </c>
+      <c r="R109" s="7">
+        <v>48</v>
+      </c>
+      <c r="S109" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T109" s="6">
+        <v>0</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.35830908082031998</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.0102154982051253</v>
+      </c>
+      <c r="W109" s="6">
+        <v>-0.011329792655168898</v>
+      </c>
+      <c r="X109" s="8">
+        <v>23.090471428571426</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>4.240136734693877</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>8.3023857142857143</v>
+      </c>
       <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="AD109" s="8">
+        <v>19.826185714285714</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>1</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>0</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14879,7 +15275,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15232,7 +15628,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -18686,7 +19082,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>44</v>
@@ -18720,25 +19116,59 @@
       <c t="s" r="N142" s="4">
         <v>52</v>
       </c>
-      <c r="O142" s="5"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="6"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="6"/>
-      <c r="T142" s="6"/>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-      <c r="X142" s="8"/>
-      <c r="Y142" s="6"/>
-      <c r="Z142" s="6"/>
-      <c r="AA142" s="8"/>
-      <c r="AB142" s="8"/>
+      <c r="O142" s="5">
+        <v>5292.0500000000002</v>
+      </c>
+      <c r="P142" s="5">
+        <v>5292.0500000000002</v>
+      </c>
+      <c r="Q142" s="6">
+        <v>0.15483906164757233</v>
+      </c>
+      <c r="R142" s="7">
+        <v>61</v>
+      </c>
+      <c r="S142" s="6">
+        <v>0.27083333333333326</v>
+      </c>
+      <c r="T142" s="6">
+        <v>0</v>
+      </c>
+      <c r="U142" s="6">
+        <v>-0.33080564242590299</v>
+      </c>
+      <c r="V142" s="6">
+        <v>0.016483971239878683</v>
+      </c>
+      <c r="W142" s="6">
+        <v>-0.0030320953127804915</v>
+      </c>
+      <c r="X142" s="8">
+        <v>22.314583333333331</v>
+      </c>
+      <c r="Y142" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="8">
+        <v>2.861945</v>
+      </c>
+      <c r="AB142" s="8">
+        <v>4.9469681818181819</v>
+      </c>
       <c r="AC142" s="8"/>
-      <c r="AD142" s="8"/>
-      <c r="AE142" s="6"/>
+      <c r="AD142" s="8">
+        <v>15.606250000000001</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF142" s="9"/>
-      <c r="AG142" s="5"/>
+      <c r="AG142" s="5">
+        <v>0</v>
+      </c>
       <c r="AH142" s="10">
         <v>2</v>
       </c>
@@ -19434,7 +19864,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>44</v>
@@ -19470,25 +19900,59 @@
       <c t="s" r="N148" s="4">
         <v>52</v>
       </c>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="7"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="8"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-      <c r="AA148" s="8"/>
-      <c r="AB148" s="8"/>
+      <c r="O148" s="5">
+        <v>5244.1400000000003</v>
+      </c>
+      <c r="P148" s="5">
+        <v>5244.1400000000003</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>-0.086914885466942371</v>
+      </c>
+      <c r="R148" s="7">
+        <v>61</v>
+      </c>
+      <c r="S148" s="6">
+        <v>-0.11594202898550721</v>
+      </c>
+      <c r="T148" s="6">
+        <v>0.00068648052874255836</v>
+      </c>
+      <c r="U148" s="6">
+        <v>-0.27938804074643314</v>
+      </c>
+      <c r="V148" s="6">
+        <v>0.066529402342424104</v>
+      </c>
+      <c r="W148" s="6">
+        <v>0.028280995549317907</v>
+      </c>
+      <c r="X148" s="8">
+        <v>43.457724390243897</v>
+      </c>
+      <c r="Y148" s="6">
+        <v>0.34146341463414637</v>
+      </c>
+      <c r="Z148" s="6">
+        <v>0.65853658536585369</v>
+      </c>
+      <c r="AA148" s="8">
+        <v>6.9279661016949152</v>
+      </c>
+      <c r="AB148" s="8">
+        <v>16.781300000000002</v>
+      </c>
       <c r="AC148" s="8"/>
-      <c r="AD148" s="8"/>
-      <c r="AE148" s="6"/>
+      <c r="AD148" s="8">
+        <v>31.811382926829268</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>0.17073170731707318</v>
+      </c>
       <c r="AF148" s="9"/>
-      <c r="AG148" s="5"/>
+      <c r="AG148" s="5">
+        <v>0</v>
+      </c>
       <c r="AH148" s="10">
         <v>2</v>
       </c>
@@ -21136,7 +21600,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -21172,25 +21636,59 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
+      <c r="O162" s="5">
+        <v>4086.5100000000002</v>
+      </c>
+      <c r="P162" s="5">
+        <v>4086.5100000000002</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.25773100375447511</v>
+      </c>
+      <c r="R162" s="7">
+        <v>41</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.3970588235294118</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.30844402681016314</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.023562991403422481</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.051933312288480873</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.03252065943800455</v>
+      </c>
+      <c r="X162" s="8">
+        <v>27.001923076923074</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>8.7004175000000004</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>7.2519230769230774</v>
+      </c>
       <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="AD162" s="8">
+        <v>23.43525769230769</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.80769230769230771</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-209.90000000000001</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -22767,7 +23265,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22803,25 +23301,59 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
+      <c r="O175" s="5">
+        <v>2719.6100000000001</v>
+      </c>
+      <c r="P175" s="5">
+        <v>2719.6100000000001</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.10256992390365727</v>
+      </c>
+      <c r="R175" s="7">
+        <v>34</v>
+      </c>
+      <c r="S175" s="6">
+        <v>-0.05555555555555558</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.37809549898698713</v>
+      </c>
+      <c r="U175" s="6">
+        <v>0.026159008093072169</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.030349020631634679</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.01900732090262942</v>
+      </c>
+      <c r="X175" s="8">
+        <v>28.428705555555556</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>9.9716666666666658</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>1.4435166666666666</v>
+      </c>
       <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="AD175" s="8">
+        <v>18.342594444444444</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.72222222222222221</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-4.9000000000000004</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -23509,7 +24041,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23545,25 +24077,59 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
+      <c r="O181" s="5">
+        <v>2344.5999999999999</v>
+      </c>
+      <c r="P181" s="5">
+        <v>2344.5999999999999</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>-0.074977117065934351</v>
+      </c>
+      <c r="R181" s="7">
+        <v>28</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.076923076923076872</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.0017273735391964513</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.31255224771816087</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.15513221871534591</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.10778512326196367</v>
+      </c>
+      <c r="X181" s="8">
+        <v>13.076985714285714</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>3.0942517241379308</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>1.1694500000000001</v>
+      </c>
       <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="AD181" s="8">
+        <v>9.8499999999999996</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -24221,7 +24787,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -24257,25 +24823,59 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
+      <c r="O187" s="5">
+        <v>1615.6500000000001</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1615.6500000000001</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.23681015791437754</v>
+      </c>
+      <c r="R187" s="7">
+        <v>18</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.37931034482758619</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.34338501531891186</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.18949401169807817</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.091106365858942218</v>
+      </c>
+      <c r="X187" s="8">
+        <v>41.606407692307691</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>9.9583333333333339</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>14.256407692307693</v>
+      </c>
       <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="AD187" s="8">
+        <v>27.887176923076922</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.15384615384615385</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-139.19999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24580,7 +25180,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24616,25 +25216,59 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
+      <c r="O190" s="5">
+        <v>3157.4200000000001</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3157.4200000000001</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.0463962984439934</v>
+      </c>
+      <c r="R190" s="7">
+        <v>40</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.030623832116094787</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.4815981719251794</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.060528849503708723</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.026475730184771111</v>
+      </c>
+      <c r="X190" s="8">
+        <v>21.136111111111109</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>3.7901941176470588</v>
+      </c>
       <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="AD190" s="8">
+        <v>14.149072222222223</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.94444444444444442</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-143.56</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -25780,7 +26414,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25816,25 +26450,59 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
+      <c r="O200" s="5">
+        <v>1226.3399999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1226.3399999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.026845584325924432</v>
+      </c>
+      <c r="R200" s="7">
+        <v>14</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.066666666666666652</v>
+      </c>
+      <c r="T200" s="6">
+        <v>1.1261802599605331</v>
+      </c>
+      <c r="U200" s="6">
+        <v>0.72090113671575584</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.27342458045892659</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.19048673287995174</v>
+      </c>
+      <c r="X200" s="8">
+        <v>18.236116666666668</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>5.148715384615385</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>2.3722166666666666</v>
+      </c>
       <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="AD200" s="8">
+        <v>14.211116666666667</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>1</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>0</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -26244,10 +26912,10 @@
         <v>-0.24444444444444446</v>
       </c>
       <c r="T204" s="6">
-        <v>0.39532169772986903</v>
+        <v>0.43621943833232391</v>
       </c>
       <c r="U204" s="6">
-        <v>0.077135349183105509</v>
+        <v>0.1182017587573697</v>
       </c>
       <c r="V204" s="6">
         <v>0.041048469329080836</v>
@@ -26577,7 +27245,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -26613,25 +27281,55 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>2587.75</v>
+      </c>
+      <c r="P207" s="5">
+        <v>2587.75</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>27</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
+      <c r="T207" s="6">
+        <v>0</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.3782359192348565</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.030098541203748431</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.016528837793449908</v>
+      </c>
+      <c r="X207" s="8">
+        <v>29.268181818181816</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.7791678571428573</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>7.8816699999999997</v>
+      </c>
       <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="AD207" s="8">
+        <v>21.787881818181816</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.36363636363636365</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-2587.75</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 810.682,22</t>
-  </si>
-  <si>
-    <t>R$ 4.503,79
-R$ 4.583,23</t>
-  </si>
-  <si>
-    <t>2.7%
-4.5%</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>(3.2%)</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>54.9%</t>
+173</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 822.712,40</t>
+  </si>
+  <si>
+    <t>R$ 4.495,70
+R$ 4.573,29</t>
+  </si>
+  <si>
+    <t>2.6%
+4.3%</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>(3.4%)</t>
+  </si>
+  <si>
+    <t>96.6%</t>
+  </si>
+  <si>
+    <t>56.7%</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -947,34 +947,34 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.1</t>
-  </si>
-  <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>8.1%</t>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>6.7</t>
-  </si>
-  <si>
-    <t>11.4</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>75.7%</t>
-  </si>
-  <si>
-    <t>-R$ 28.969,47</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>18.1</t>
+  </si>
+  <si>
+    <t>75.3%</t>
+  </si>
+  <si>
+    <t>-R$ 29.226,07</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>-0.12857142857142856</v>
       </c>
       <c r="T7" s="6">
-        <v>0.35816128153912646</v>
+        <v>0.37781650516679005</v>
       </c>
       <c r="U7" s="6">
-        <v>0.0089692886833301275</v>
+        <v>0.028624512310993732</v>
       </c>
       <c r="V7" s="6">
         <v>0.053677208429093959</v>
@@ -2947,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2983,25 +2983,59 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
+      <c r="O13" s="5">
+        <v>6454.0200000000004</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6454.0200000000004</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.066276107492986958</v>
+      </c>
+      <c r="R13" s="7">
+        <v>66</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.043478260869565188</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.37333692799216606</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.034998961887319838</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.028685997254424372</v>
+      </c>
+      <c r="W13" s="6">
+        <v>-0.0012875696077793376</v>
+      </c>
+      <c r="X13" s="8">
+        <v>31.657091489361701</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.74468085106382975</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.1702127659574468</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>4.879040909090909</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>8.8581553191489366</v>
+      </c>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="AD13" s="8">
+        <v>20.663121276595746</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.46808510638297873</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-84.900000000000006</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -4787,7 +4821,9 @@
       <c r="AB27" s="8">
         <v>12.796235483870968</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>16.796773000000002</v>
+      </c>
       <c r="AD27" s="8">
         <v>19.009999999999998</v>
       </c>
@@ -4916,7 +4952,9 @@
       <c r="AB28" s="8">
         <v>6.9856310344827586</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>11.755746</v>
+      </c>
       <c r="AD28" s="8">
         <v>18.710920689655175</v>
       </c>
@@ -6319,7 +6357,9 @@
       <c r="AB39" s="8">
         <v>3.3333347826086959</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>5.6489890000000003</v>
+      </c>
       <c r="AD39" s="8">
         <v>11.290403030303031</v>
       </c>
@@ -6710,7 +6750,9 @@
       <c r="AB42" s="8">
         <v>11.131480555555555</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>19.216203</v>
+      </c>
       <c r="AD42" s="8">
         <v>26.162963888888889</v>
       </c>
@@ -7228,7 +7270,9 @@
       <c r="AB46" s="8">
         <v>16.091463414634145</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>27.742681999999999</v>
+      </c>
       <c r="AD46" s="8">
         <v>34.68292682926829</v>
       </c>
@@ -7746,7 +7790,9 @@
       <c r="AB50" s="8">
         <v>4.9245605263157897</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>7.4635959999999999</v>
+      </c>
       <c r="AD50" s="8">
         <v>15.41622894736842</v>
       </c>
@@ -8361,7 +8407,9 @@
       <c r="AB55" s="8">
         <v>6.7692973684210527</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>9.6297139999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>16.600876315789474</v>
       </c>
@@ -10367,7 +10415,9 @@
       <c r="AB71" s="8">
         <v>6.5472233333333332</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>8.7482970000000009</v>
+      </c>
       <c r="AD71" s="8">
         <v>16.266667741935485</v>
       </c>
@@ -10845,7 +10895,9 @@
       <c r="AB75" s="8">
         <v>8.7257545454545458</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>12.592423</v>
+      </c>
       <c r="AD75" s="8">
         <v>19.5303</v>
       </c>
@@ -12688,7 +12740,9 @@
       <c r="AB90" s="8">
         <v>14.029708695652173</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>18.447825000000002</v>
+      </c>
       <c r="AD90" s="8">
         <v>25.385508695652174</v>
       </c>
@@ -14124,7 +14178,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14160,25 +14214,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>3242.4099999999999</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3242.4099999999999</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.16106238195037392</v>
+      </c>
+      <c r="R102" s="7">
+        <v>31</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.13888888888888884</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.32366832078608199</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.034546710625738268</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.018241986670408741</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0058080255118877627</v>
+      </c>
+      <c r="X102" s="8">
+        <v>54.891113333333337</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>9.1655566666666672</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>25.173807142857139</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>33.143808999999997</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>37.997779999999999</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.26666666666666666</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -15041,7 +15131,9 @@
       <c r="AB109" s="8">
         <v>8.3023857142857143</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>11.890475</v>
+      </c>
       <c r="AD109" s="8">
         <v>19.826185714285714</v>
       </c>
@@ -15263,7 +15355,9 @@
       <c r="AB111" s="8">
         <v>1.871209090909091</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>6.3045450000000001</v>
+      </c>
       <c r="AD111" s="8">
         <v>13.483336363636363</v>
       </c>
@@ -16231,7 +16325,9 @@
       <c r="AB119" s="8">
         <v>5.2677800000000001</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>7.7733319999999999</v>
+      </c>
       <c r="AD119" s="8">
         <v>14.721113333333333</v>
       </c>
@@ -17156,7 +17252,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18333,7 +18429,7 @@
         <v>-253.59999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -19158,7 +19254,9 @@
       <c r="AB142" s="8">
         <v>4.9469681818181819</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>7.569191</v>
+      </c>
       <c r="AD142" s="8">
         <v>15.606250000000001</v>
       </c>
@@ -19942,7 +20040,9 @@
       <c r="AB148" s="8">
         <v>16.781300000000002</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>23.893901</v>
+      </c>
       <c r="AD148" s="8">
         <v>31.811382926829268</v>
       </c>
@@ -20611,7 +20711,7 @@
         <v>-2324.1300000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21678,7 +21778,9 @@
       <c r="AB162" s="8">
         <v>7.2519230769230774</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>15.313651</v>
+      </c>
       <c r="AD162" s="8">
         <v>23.43525769230769</v>
       </c>
@@ -21821,7 +21923,7 @@
         <v>-449.79000000000002</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -23343,7 +23445,9 @@
       <c r="AB175" s="8">
         <v>1.4435166666666666</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>11.382406</v>
+      </c>
       <c r="AD175" s="8">
         <v>18.342594444444444</v>
       </c>
@@ -24119,7 +24223,9 @@
       <c r="AB181" s="8">
         <v>1.1694500000000001</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>4.5050499999999998</v>
+      </c>
       <c r="AD181" s="8">
         <v>9.8499999999999996</v>
       </c>
@@ -24865,7 +24971,9 @@
       <c r="AB187" s="8">
         <v>14.256407692307693</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>20.933333000000001</v>
+      </c>
       <c r="AD187" s="8">
         <v>27.887176923076922</v>
       </c>
@@ -25258,7 +25366,9 @@
       <c r="AB190" s="8">
         <v>3.7901941176470588</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>7.5489670000000002</v>
+      </c>
       <c r="AD190" s="8">
         <v>14.149072222222223</v>
       </c>
@@ -25926,7 +26036,7 @@
         <v>19945</v>
       </c>
       <c r="B196" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C196" s="4">
         <v>44</v>
@@ -25962,25 +26072,61 @@
       <c t="s" r="N196" s="4">
         <v>52</v>
       </c>
-      <c r="O196" s="5"/>
-      <c r="P196" s="5"/>
-      <c r="Q196" s="6"/>
-      <c r="R196" s="7"/>
-      <c r="S196" s="6"/>
-      <c r="T196" s="6"/>
-      <c r="U196" s="6"/>
-      <c r="V196" s="6"/>
-      <c r="W196" s="6"/>
-      <c r="X196" s="8"/>
-      <c r="Y196" s="6"/>
-      <c r="Z196" s="6"/>
-      <c r="AA196" s="8"/>
-      <c r="AB196" s="8"/>
-      <c r="AC196" s="8"/>
-      <c r="AD196" s="8"/>
-      <c r="AE196" s="6"/>
+      <c r="O196" s="5">
+        <v>2333.75</v>
+      </c>
+      <c r="P196" s="5">
+        <v>2333.75</v>
+      </c>
+      <c r="Q196" s="6">
+        <v>-0.25971451229183184</v>
+      </c>
+      <c r="R196" s="7">
+        <v>29</v>
+      </c>
+      <c r="S196" s="6">
+        <v>-0.40816326530612246</v>
+      </c>
+      <c r="T196" s="6">
+        <v>9.3025878521692569</v>
+      </c>
+      <c r="U196" s="6">
+        <v>9.3025878521692569</v>
+      </c>
+      <c r="V196" s="6">
+        <v>0.07410112479914302</v>
+      </c>
+      <c r="W196" s="6">
+        <v>0.030518907337975361</v>
+      </c>
+      <c r="X196" s="8">
+        <v>28.38335</v>
+      </c>
+      <c r="Y196" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z196" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="8">
+        <v>7.4666652173913048</v>
+      </c>
+      <c r="AB196" s="8">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="AC196" s="8">
+        <v>11.088333</v>
+      </c>
+      <c r="AD196" s="8">
+        <v>15.6</v>
+      </c>
+      <c r="AE196" s="6">
+        <v>1</v>
+      </c>
       <c r="AF196" s="9"/>
-      <c r="AG196" s="5"/>
+      <c r="AG196" s="5">
+        <v>-171.69999999999999</v>
+      </c>
       <c r="AH196" s="10">
         <v>1</v>
       </c>
@@ -26492,7 +26638,9 @@
       <c r="AB200" s="8">
         <v>2.3722166666666666</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>7.2472219999999998</v>
+      </c>
       <c r="AD200" s="8">
         <v>14.211116666666667</v>
       </c>
@@ -27319,7 +27467,9 @@
       <c r="AB207" s="8">
         <v>7.8816699999999997</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>16.01361</v>
+      </c>
       <c r="AD207" s="8">
         <v>21.787881818181816</v>
       </c>
@@ -27864,7 +28014,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 822.712,40</t>
-  </si>
-  <si>
-    <t>R$ 4.495,70
-R$ 4.573,29</t>
-  </si>
-  <si>
-    <t>2.6%
-4.3%</t>
+174</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 826.597,29</t>
+  </si>
+  <si>
+    <t>R$ 4.492,38
+R$ 4.569,33</t>
+  </si>
+  <si>
+    <t>2.4%
+4.2%</t>
   </si>
   <si>
     <t>49.1</t>
   </si>
   <si>
-    <t>(3.4%)</t>
-  </si>
-  <si>
-    <t>96.6%</t>
-  </si>
-  <si>
-    <t>56.7%</t>
+    <t>(3.6%)</t>
+  </si>
+  <si>
+    <t>96.3%</t>
+  </si>
+  <si>
+    <t>56.5%</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -947,10 +947,10 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>72.9%</t>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>72.8%</t>
   </si>
   <si>
     <t>8.3%</t>
@@ -974,7 +974,7 @@
     <t>-R$ 29.226,07</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -2213,10 +2213,10 @@
         <v>-0.12857142857142856</v>
       </c>
       <c r="T7" s="6">
-        <v>0.37781650516679005</v>
+        <v>0.3634866455564843</v>
       </c>
       <c r="U7" s="6">
-        <v>0.028624512310993732</v>
+        <v>0.014294652700687952</v>
       </c>
       <c r="V7" s="6">
         <v>0.053677208429093959</v>
@@ -16859,7 +16859,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -21084,9 +21084,7 @@
       <c r="AB156" s="8">
         <v>3.9439393939393943</v>
       </c>
-      <c r="AC156" s="8">
-        <v>12.42188</v>
-      </c>
+      <c r="AC156" s="8"/>
       <c r="AD156" s="8">
         <v>19.138235294117649</v>
       </c>
@@ -25941,7 +25939,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25977,25 +25975,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>3884.8899999999999</v>
+      </c>
+      <c r="P195" s="5">
+        <v>3884.8899999999999</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.167119029242775</v>
+      </c>
+      <c r="R195" s="7">
+        <v>46</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.33951656288852455</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.025762505502086291</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.035384013446970182</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0053136639647454629</v>
+      </c>
+      <c r="X195" s="8">
+        <v>24.915384615384614</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.7570377777777777</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>6.7153320000000001</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>17.661538461538463</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.80769230769230771</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>0</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-17).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 826.597,29</t>
-  </si>
-  <si>
-    <t>R$ 4.492,38
-R$ 4.569,33</t>
-  </si>
-  <si>
-    <t>2.4%
-4.2%</t>
-  </si>
-  <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>(3.6%)</t>
-  </si>
-  <si>
-    <t>96.3%</t>
-  </si>
-  <si>
-    <t>56.5%</t>
+176</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 838.462,22</t>
+  </si>
+  <si>
+    <t>R$ 4.507,86
+R$ 4.584,82</t>
+  </si>
+  <si>
+    <t>2.6%
+4.4%</t>
+  </si>
+  <si>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>(3.4%)</t>
+  </si>
+  <si>
+    <t>95.6%</t>
+  </si>
+  <si>
+    <t>55.8%</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -947,31 +947,31 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.2</t>
-  </si>
-  <si>
-    <t>72.8%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>72.3%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
   </si>
   <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>11.7</t>
-  </si>
-  <si>
-    <t>18.1</t>
-  </si>
-  <si>
-    <t>75.3%</t>
-  </si>
-  <si>
-    <t>-R$ 29.226,07</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>11.8</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>-R$ 29.785,22</t>
   </si>
   <si>
     <t>2.95</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>8.8581553191489366</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>13.786879000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>20.663121276595746</v>
       </c>
@@ -5708,10 +5710,10 @@
         <v>0.32876712328767121</v>
       </c>
       <c r="T34" s="6">
-        <v>-2.2061441784910865</v>
+        <v>-2.1734764972046716</v>
       </c>
       <c r="U34" s="6">
-        <v>-2.5060893480299464</v>
+        <v>-2.4734216667435316</v>
       </c>
       <c r="V34" s="6">
         <v>0.082996305349300775</v>
@@ -8720,7 +8722,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8756,25 +8758,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>5793.6899999999996</v>
+      </c>
+      <c r="P58" s="5">
+        <v>5793.6899999999996</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.11677840188439936</v>
+      </c>
+      <c r="R58" s="7">
+        <v>72</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.27330728775616231</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.080586344799255749</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.014992517721866376</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0019724907615008744</v>
+      </c>
+      <c r="X58" s="8">
+        <v>37.634482758620692</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.43103448275862066</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.7065732394366195</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>18.283332758620688</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>21.240228999999999</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>28.170689655172417</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.27586206896551724</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-287.44999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -10948,7 +10986,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10982,25 +11020,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>6071.2399999999998</v>
+      </c>
+      <c r="P76" s="5">
+        <v>6071.2399999999998</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.27223920755895215</v>
+      </c>
+      <c r="R76" s="7">
+        <v>72</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.013698630136986356</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.53781290148305783</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.12877784439422588</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.022111710293119691</v>
+      </c>
+      <c r="W76" s="6">
+        <v>-0.010319885229376536</v>
+      </c>
+      <c r="X76" s="8">
+        <v>21.522221212121213</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>2.6763888888888889</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>3.3516649999999997</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>5.9935700000000001</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>12.719696969696969</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.93939393939393945</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-271.69999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -21084,7 +21158,9 @@
       <c r="AB156" s="8">
         <v>3.9439393939393943</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>12.42188</v>
+      </c>
       <c r="AD156" s="8">
         <v>19.138235294117649</v>
       </c>
@@ -23963,7 +24039,9 @@
       <c r="AB179" s="8">
         <v>2.7103448275862068</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>8.3999989999999993</v>
+      </c>
       <c r="AD179" s="8">
         <v>15.3477</v>
       </c>
